--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_220_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_220_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>1</v>
@@ -2119,16 +2119,16 @@
         <v>12</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>8</v>
@@ -2511,7 +2511,7 @@
         <v>11</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2707,10 +2707,10 @@
         <v>19</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>109</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
         <v>24</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>10</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>3</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6056,10 +6056,10 @@
         <v>15</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
         <v>14</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>55</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X48" t="n">
         <v>19</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_220_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_220_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="P2" t="n">
         <v>10</v>
@@ -833,10 +833,10 @@
         <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
         <v>12</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3839,10 +3839,10 @@
         <v>4</v>
       </c>
       <c r="X30" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -5480,14 +5480,14 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,10 +5676,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>2</v>
       </c>
       <c r="X48" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="Y48" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA48" t="n">
